--- a/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_Value_Unfairness_of_sensitive_attribute.xlsx
+++ b/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_Value_Unfairness_of_sensitive_attribute.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,46 +441,116 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>P-Value</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Significance</t>
+          <t>P-Value (raw)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-Value (Bonferroni)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Reject (Bonf@0.05)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Partial_R2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cohen_f2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (raw)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (bonf)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mean Rating</t>
+          <t>Number of Items</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.16634273672879</v>
+        <v>0.1438957297795987</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01653890287907109</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>*</t>
+        <v>10.28587180405277</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.643182188182107e-23</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.615000814000636e-22</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1073232390474738</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3867994006695197</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Number of Items</t>
+          <t>Number of Ratings</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.151223602818587</v>
+        <v>-0.2033245274686142</v>
       </c>
       <c r="C3" t="n">
-        <v>2.026820315819761e-15</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>-8.452544615449959</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.173176433416854e-16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.580988153517079e-15</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.07509154196378057</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2706344281511328</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -489,120 +559,244 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dataset_BX</t>
+          <t>Number of Users</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1338094798345106</v>
+        <v>0.06639223282065441</v>
       </c>
       <c r="C4" t="n">
-        <v>1.804832398136049e-05</v>
-      </c>
-      <c r="D4" t="inlineStr">
+        <v>4.078871289340164</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.936014710540167e-05</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.001085923236318837</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01855509805090853</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.06687368802092193</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>***</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>hit@5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.111131477963565</v>
+        <v>-0.02317140456976889</v>
       </c>
       <c r="C5" t="n">
-        <v>1.542268147370768e-06</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>-3.6745099094597</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0002527150370062306</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.005559730814137074</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01511135143069334</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.05446221832825176</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>***</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Age</t>
+          <t>Rating per User</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07689560413496224</v>
+        <v>0.0328531479636862</v>
       </c>
       <c r="C6" t="n">
-        <v>1.056841044494637e-09</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>3.484718397387927</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0005169802572104968</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01137356565863093</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01361133667889172</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.04905607505358169</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>***</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Number of Users</t>
+          <t>Mean Rating</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06765208752621001</v>
+        <v>0.1595061909769637</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001312039577008569</v>
-      </c>
-      <c r="D7" t="inlineStr">
+        <v>2.973330370588122</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.00302622650439204</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.06657698309662488</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.009946319466903084</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.03584713285595013</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Gender</t>
+          <t>Gini User</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03423587382860172</v>
+        <v>0.02957200743720428</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002525976477343768</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
+        <v>2.114539290814094</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03474988037683379</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7644973682903434</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00505530991411391</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.01821964061402382</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Difference between Sensitive Attribute Percentage</t>
+          <t>Standart Deviation of Rating</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02999334840209232</v>
+        <v>-0.05459011929680031</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2644848152916993</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>-1.919129533668781</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05529109826124774</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00416784969787632</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01502118068302138</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gini User</t>
+          <t>Density</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02993688330486002</v>
+        <v>-0.03529721057519514</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09646404153032533</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>-1.758415131623722</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.07902447548726599</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.003501360777674341</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01261911457716181</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -611,160 +805,416 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02645172996171173</v>
+        <v>0.02441748536790913</v>
       </c>
       <c r="C11" t="n">
-        <v>0.230566067969001</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>1.424948862434984</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1545265360032246</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.00230205112895531</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.00829673055801668</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rating per User</t>
+          <t>Skewness of Long Tail Items</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02596603746260353</v>
+        <v>0.009364009928853181</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03316685805473615</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.9852999746192642</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3247475645771581</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001101984336267344</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.003971617746524209</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Skewness of Popularity Bias</t>
+          <t>Difference between Sensitive Attribute Percentage</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0103571328724483</v>
+        <v>0.02032981841270298</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4050291809514628</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>0.9736484975730221</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.330498651642595</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001076103704286871</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.003878342394160243</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skewness of Long Tail Items</t>
+          <t>Skewness of Popularity Bias</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01021531086090074</v>
+        <v>0.009096421778724412</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4037619092439281</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>0.9320399819176851</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3515714970912474</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.000986183899308588</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.003554266015338552</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hit@5</t>
+          <t>Sensitive Feature_Age</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.006200088587464818</v>
+        <v>102698210491.1156</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2209968724063879</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>0.8507683939003652</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3951294497719184</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0008218318324337226</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.002961931293332312</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gini Item</t>
+          <t>Sensitive Feature_Gender</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002432769186862443</v>
+        <v>102698210491.0729</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9281880390242319</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>0.8507683939000107</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3951294497721151</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0008218318324330383</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.002961931293329845</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Dataset_ml1m</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001230206406261689</v>
+        <v>-30931848555.62001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9512779229844177</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>-0.8507683938999869</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3951294497721284</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0008218318324329923</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.00296193129332968</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Model Name_FOCF</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.01665772912602233</v>
+        <v>-20741315368.95157</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5226347196459827</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>-0.8507683938990106</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3951294497726705</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0008218318324311077</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.002961931293322888</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dataset_ml1m</t>
+          <t>Model Name_PFCN_MLP</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02267800187094642</v>
+        <v>-20741315368.93851</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6063820524335202</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>-0.8507683938984787</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.395129449772966</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.000821831832430081</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.002961931293319187</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Standart Deviation of Rating</t>
+          <t>const</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.05571506592936905</v>
+        <v>-51025046566.35547</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1289050003889046</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>-0.8507683938979581</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.3951294497732551</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0008218318324290759</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.002961931293315565</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Number of Ratings</t>
+          <t>Model Name_NFCF</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.216596339591008</v>
+        <v>-20741315368.9111</v>
       </c>
       <c r="C21" t="n">
-        <v>1.723906276974184e-11</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>-0.8507683938973554</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.3951294497735898</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0008218318324279125</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.002961931293311372</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-30931848555.49377</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.8507683938965439</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.3951294497740404</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.000821831832426346</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.002961931293305726</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gini Item</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.006026537854608091</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2857410091869663</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.7751437378848389</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.277312454333329e-05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0003343599139392977</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shape</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.002502629430201429</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1598984033308661</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8729977999491338</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.905313246797017e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.000104709234699971</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
